--- a/incubator_CLEANED.xlsx
+++ b/incubator_CLEANED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2829e137101a93ae/Desktop/IIM Intern/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{DD704A73-1567-4DEB-9542-7B486BD04C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF66A16C-80AF-4A4B-97D4-C93107E3C6F6}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{DD704A73-1567-4DEB-9542-7B486BD04C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09296C30-795B-4FE8-B54B-E00D0ED26E59}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="573">
   <si>
     <t>Incubator</t>
   </si>
@@ -1751,9 +1751,6 @@
   </si>
   <si>
     <t>Insufficient Dataset</t>
-  </si>
-  <si>
-    <t>Website link</t>
   </si>
   <si>
     <t>TBI BITS Pilani</t>
@@ -16214,7 +16211,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D28E25-A11D-4D9B-AFD2-20C01892F415}">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="78.765625" bestFit="1" customWidth="1"/>
@@ -16222,18 +16219,15 @@
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="str">
         <f>Sheet2!A33</f>
         <v>NASSCOM 10,000 Startups</v>
@@ -16243,7 +16237,7 @@
         <v>57.689869296060749</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="str">
         <f>Sheet2!A11</f>
         <v>CIIE IIM-A</v>
@@ -16253,7 +16247,7 @@
         <v>44.804525527410718</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="str">
         <f>Sheet2!A99</f>
         <v>T-Hub</v>
@@ -16263,7 +16257,7 @@
         <v>43.664805521087523</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="str">
         <f>Sheet2!A101</f>
         <v>SINE (Society for Innovation &amp; Entrepreneurship) - IIT Bombay</v>
@@ -16273,7 +16267,7 @@
         <v>42.152850797492562</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="str">
         <f>Sheet2!A21</f>
         <v>IIT Madras Incubation Cell (IITMIC)</v>
@@ -16283,7 +16277,7 @@
         <v>39.45622740588032</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="str">
         <f>Sheet2!A17</f>
         <v>Foundation For Innovation And Technology Transfer, IIT-D</v>
@@ -16293,7 +16287,7 @@
         <v>35.266202089635541</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="str">
         <f>Sheet2!A29</f>
         <v>Life Science Incubator at IKP Knowledge Park</v>
@@ -16303,7 +16297,7 @@
         <v>33.433264153476358</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="str">
         <f>Sheet2!A37</f>
         <v>NSRCEL, IIM Bangalore</v>
@@ -16313,7 +16307,7 @@
         <v>32.111103845303411</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="str">
         <f>Sheet2!A28</f>
         <v>Kerala Startup Mission KSUM</v>
@@ -16323,7 +16317,7 @@
         <v>31.865273459903769</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="str">
         <f>Sheet2!A102</f>
         <v>Maker Village - Kochi</v>
@@ -16333,7 +16327,7 @@
         <v>31.039531174805425</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="str">
         <f>Sheet2!A6</f>
         <v>Bio Incubator at C-CAMP</v>
@@ -16343,7 +16337,7 @@
         <v>27.33383070546229</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="str">
         <f>Sheet2!A19</f>
         <v>IIM Calcutta Innovation Park</v>
@@ -16353,7 +16347,7 @@
         <v>25.42607005320091</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="str">
         <f>Sheet2!A62</f>
         <v>Venture Center</v>
@@ -16363,7 +16357,7 @@
         <v>24.577253672389237</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="str">
         <f>Sheet2!A87</f>
         <v>STEP- IIT Roorkee</v>
@@ -16373,7 +16367,7 @@
         <v>24.033742039461764</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="str">
         <f>Sheet2!A79</f>
         <v>MITCON Biotechnology Business Incubation Centre</v>
@@ -16425,7 +16419,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B21" s="4">
         <f>Sheet2!L51</f>
